--- a/data/trans_orig/KIDMED_R3-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KIDMED_R3-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>79579</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>61039</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89955</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>64,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>49,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>73,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>76942</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>68812</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>84991</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>67,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>82982</t>
+          <t>79987</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62707</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97607</t>
+          <t>88571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>159924</t>
+          <t>159565</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135241</t>
+          <t>138693</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174962</t>
+          <t>172158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43317</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32941</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61857</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>37309</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29260</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>45439</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32,66%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53833</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39208</t>
+          <t>30027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74108</t>
+          <t>48059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>91142</t>
+          <t>81929</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76104</t>
+          <t>69336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115825</t>
+          <t>102801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>163958</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>148753</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>175598</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>70,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>75,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>126857</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>111818</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>137742</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>68,16%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>60,08%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>74,01%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>170934</t>
+          <t>128224</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154410</t>
+          <t>118211</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184135</t>
+          <t>139238</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>297791</t>
+          <t>292181</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>277319</t>
+          <t>273836</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>316011</t>
+          <t>307599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>74,69%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55643</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82488</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>59257</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48372</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74296</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31,84%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>39,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>76586</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63385</t>
+          <t>41355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93110</t>
+          <t>62382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>135843</t>
+          <t>119652</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117623</t>
+          <t>104234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156315</t>
+          <t>137997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84763</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72034</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>97109</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,26%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>85884</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>52389</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>106437</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>45,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>93457</t>
+          <t>82092</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80527</t>
+          <t>71648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107744</t>
+          <t>92601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>179342</t>
+          <t>166856</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136948</t>
+          <t>151018</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204660</t>
+          <t>186180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>81759</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69413</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>94488</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>56,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>102365</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81812</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>135860</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>54,38%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>43,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>72,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89632</t>
+          <t>72946</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75345</t>
+          <t>62437</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102562</t>
+          <t>83390</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>191997</t>
+          <t>154704</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166679</t>
+          <t>135380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234391</t>
+          <t>170542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>110722</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>99750</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>120854</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>66,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>60,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>72,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>104330</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>93621</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>114800</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>56,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>69,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>118743</t>
+          <t>103337</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106447</t>
+          <t>92638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129310</t>
+          <t>113510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>223073</t>
+          <t>214059</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>206819</t>
+          <t>198552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237053</t>
+          <t>228668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55443</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45311</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>66415</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>33,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>39,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>60189</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>49719</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>70898</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>43,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>58566</t>
+          <t>60642</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47999</t>
+          <t>50469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70862</t>
+          <t>71341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>118755</t>
+          <t>116085</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104775</t>
+          <t>101476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135009</t>
+          <t>131592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>439023</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>411473</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>463185</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>585</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>394014</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>342979</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>421661</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>60,33%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>52,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393640</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>435981</t>
+          <t>374528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>495052</t>
+          <t>412911</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>860130</t>
+          <t>832662</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>796725</t>
+          <t>798965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>899449</t>
+          <t>863679</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>247801</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>223639</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>275351</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>259120</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>231473</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>310155</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>39,67%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>47,49%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>278617</t>
+          <t>224568</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249681</t>
+          <t>205297</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>308752</t>
+          <t>243680</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>537737</t>
+          <t>472369</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>498418</t>
+          <t>441352</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>601142</t>
+          <t>506066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
